--- a/templates/Шаблон_спецификации_РД_ИИ.xlsx
+++ b/templates/Шаблон_спецификации_РД_ИИ.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Наименование</t>
   </si>
   <si>
-    <t xml:space="preserve">Модель / ГОСТ</t>
+    <t xml:space="preserve">Модель / ГОСТ / ТУ</t>
   </si>
   <si>
     <t xml:space="preserve">Артикул / Код</t>
@@ -219,57 +219,53 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -568,7 +564,7 @@
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6"/>
     </row>
-    <row r="2" customFormat="false" ht="28.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -597,7 +593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="12" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="10"/>
